--- a/packages/content-extraction/test/fixtures/policy.xlsx
+++ b/packages/content-extraction/test/fixtures/policy.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Environment</t>
   </si>
@@ -26,6 +26,12 @@
   </si>
   <si>
     <t>The team leader must approve every production renewal request.</t>
+  </si>
+  <si>
+    <t>Staging</t>
+  </si>
+  <si>
+    <t>The duty manager approves a staging renewal.</t>
   </si>
 </sst>
 </file>
@@ -61,6 +67,14 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>